--- a/testData/E2E_UAT_024.xlsx
+++ b/testData/E2E_UAT_024.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Automation_Project\E2E_Automation\testData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://netapp-my.sharepoint.com/personal/sunilr2_netapp_com/Documents/Desktop/Playwright Python/E2E_Automation/testData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC6CB76C-3C15-4C6E-AC13-6AA4A107BFE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{EC6CB76C-3C15-4C6E-AC13-6AA4A107BFE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4DB1BB09-884E-43FD-B9BD-1FE52C0B56D7}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="21600" windowHeight="13749" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -105,9 +105,6 @@
     <t>Test for Automation</t>
   </si>
   <si>
-    <t>To be Determined Before Qualify Sales Stage</t>
-  </si>
-  <si>
     <t>Up-sell/Cross-sell</t>
   </si>
   <si>
@@ -174,9 +171,6 @@
     <t>Reseller</t>
   </si>
   <si>
-    <t>Rajwesh Smam</t>
-  </si>
-  <si>
     <t>Reseller through Distributor</t>
   </si>
   <si>
@@ -199,6 +193,12 @@
   </si>
   <si>
     <t>DR Override Justification</t>
+  </si>
+  <si>
+    <t>test test</t>
+  </si>
+  <si>
+    <t>To be Determined at Qualify Sales Stage</t>
   </si>
 </sst>
 </file>
@@ -699,7 +699,7 @@
       <c r="S1" s="11"/>
       <c r="T1" s="11"/>
       <c r="U1" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="V1" s="11"/>
       <c r="W1" s="11"/>
@@ -709,7 +709,7 @@
       <c r="AA1" s="11"/>
       <c r="AB1" s="11"/>
       <c r="AC1" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.4">
@@ -740,10 +740,10 @@
       </c>
       <c r="T2" s="12"/>
       <c r="U2" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="V2" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="W2" s="12"/>
       <c r="X2" s="12"/>
@@ -751,10 +751,10 @@
       <c r="Z2" s="12"/>
       <c r="AA2" s="12"/>
       <c r="AB2" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.4">
@@ -810,7 +810,7 @@
         <v>20</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S3" s="4" t="s">
         <v>21</v>
@@ -819,31 +819,31 @@
         <v>22</v>
       </c>
       <c r="U3" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V3" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="W3" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="W3" s="4" t="s">
+      <c r="X3" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="X3" s="4" t="s">
+      <c r="Y3" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="Y3" s="4" t="s">
+      <c r="Z3" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="Z3" s="4" t="s">
+      <c r="AA3" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="AA3" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="AB3" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="AC3" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.4">
@@ -860,69 +860,69 @@
         <v>25</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H4" s="10">
         <v>6121715</v>
       </c>
       <c r="I4" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="K4" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>29</v>
       </c>
       <c r="L4" s="9"/>
       <c r="M4" s="9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N4" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O4" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P4" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q4" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="R4" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="S4" s="6" t="s">
         <v>30</v>
-      </c>
-      <c r="P4" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q4" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="R4" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="S4" s="6" t="s">
-        <v>31</v>
       </c>
       <c r="T4" s="7">
         <v>1000</v>
       </c>
       <c r="U4" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V4" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="W4" s="6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="X4" s="6"/>
       <c r="Y4" s="6"/>
       <c r="Z4" s="6"/>
       <c r="AA4" s="6"/>
       <c r="AB4" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AC4" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
